--- a/Mentorias/2026-10-23_Emerson_e_Julio/02_Comparativo_FinBERT.xlsx
+++ b/Mentorias/2026-10-23_Emerson_e_Julio/02_Comparativo_FinBERT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\mestrado\coleta_dados_petr4\Mentorias\2026-10-23_Emerson_e_Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_3D6687FC98CEB09C887A3AB81025F6BCDC48D999" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_C784901BED39F3B6DA0ABA36545C7094D030CC6A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="164">
   <si>
     <t>FinBERT + GARCH/SVM/XGBoost  ×  FinBERT + Prophet</t>
   </si>
@@ -101,14 +101,20 @@
     <t>Acerto na direção do pregão seguinte — 579 pregões de teste por papel</t>
   </si>
   <si>
-    <t>O adversário é o PALPITE FIXO: quem não lê nada e sempre chuta o lado mais frequente. Verde = superou o palpite fixo. Nenhum caso teve significância estatística.</t>
+    <t>O adversário é o PALPITE FIXO: quem não lê nada, não calcula nada, e simplesmente diz sempre o mesmo lado. Há duas versões dele, explicadas abaixo da tabela — e a conclusão é a mesma nas duas. Verde = superou o palpite fixo com o gabarito na mão.</t>
   </si>
   <si>
     <t>Papel</t>
   </si>
   <si>
     <t>Palpite fixo
-(o adversário)</t>
+COM GABARITO
+(o que usei)</t>
+  </si>
+  <si>
+    <t>Palpite fixo
+DECIDIDO NO
+PASSADO</t>
   </si>
   <si>
     <t>GARCH+SVM
@@ -165,7 +171,7 @@
     <t>ABEV3</t>
   </si>
   <si>
-    <t>Supera o palpite fixo em:</t>
+    <t>Supera o palpite COM GABARITO:</t>
   </si>
   <si>
     <t>3 de 10</t>
@@ -177,13 +183,40 @@
     <t>1 de 10</t>
   </si>
   <si>
-    <t>Com significância (p&lt;0,05):</t>
+    <t>Supera o DECIDIDO NO PASSADO:</t>
+  </si>
+  <si>
+    <t>7 de 10</t>
+  </si>
+  <si>
+    <t>6 de 10</t>
+  </si>
+  <si>
+    <t>4 de 10</t>
+  </si>
+  <si>
+    <t>…desses, com significância:</t>
   </si>
   <si>
     <t>0 de 10</t>
   </si>
   <si>
-    <t>Como ler: a linha de baixo é a que decide. ZERO modelos, em ZERO papéis, superaram o palpite fixo de forma estatisticamente confiável. Os poucos casos em verde estão dentro da margem de erro — com 579 pregões, qualquer diferença menor que ~4 pontos percentuais é indistinguível de sorte.</t>
+    <t>Palpite fixo COM O GABARITO NA MÃO (a coluna amarela — foi o que usei)</t>
+  </si>
+  <si>
+    <t>Olha o próprio período de teste, vê qual lado foi mais frequente entre 2024 e 2026, e supõe que o investidor já sabia disso lá atrás. É o adversário MAIS DIFÍCIL possível, porque equivale a conhecer o futuro. Usei este de propósito: se o modelo vence ele, vence qualquer um.</t>
+  </si>
+  <si>
+    <t>Palpite fixo DECIDIDO NO PASSADO (a coluna seguinte — o adversário realista)</t>
+  </si>
+  <si>
+    <t>Escolhe o lado olhando só o treino (até 2022) — o que se saberia de verdade na época — e aplica daí em diante, sem mudar. Em 5 dos 10 papéis o treino apontava BAIXA e o teste veio ALTA, então esse palpite errou o lado e ficou abaixo de 50%. Na média, é 2,1 pontos mais fácil de vencer que o com gabarito.</t>
+  </si>
+  <si>
+    <t>E a conclusão muda? Não.</t>
+  </si>
+  <si>
+    <t>Contra o adversário mais fácil, os modelos passam em 6 ou 7 dos 10 papéis — mas só UM caso em 60 alcança significância estatística. Com 60 testes, o acaso sozinho produziria uns 3. Ou seja: continua sendo ruído, e a conclusão vale nas duas réguas.</t>
   </si>
   <si>
     <t>Previsão do tamanho do sacolejo (volatilidade)</t>
@@ -241,9 +274,6 @@
     <t>5 de 10</t>
   </si>
   <si>
-    <t>4 de 10</t>
-  </si>
-  <si>
     <t>Como ler: 'melhorou em 5 de 10' é exatamente o que cara-ou-coroa produziria. As médias ficam entre −0,14 e +0,07 ponto percentual na direção — ou seja, perto de zero. O sentimento dos comunicados da CVM, nesta forma de uso, não acrescenta poder de previsão a nenhuma das duas famílias de modelo.</t>
   </si>
   <si>
@@ -254,48 +284,270 @@
   </si>
   <si>
     <t>Valor investido
-(médio por investidor)</t>
+(médio)</t>
   </si>
   <si>
     <t>Comprar e segurar
-(%)</t>
-  </si>
-  <si>
-    <t>Comprar e segurar
-(R$)</t>
-  </si>
-  <si>
-    <t>FinBERT+GARCH
-(%)</t>
-  </si>
-  <si>
-    <t>FinBERT+GARCH
-(R$)</t>
-  </si>
-  <si>
-    <t>FinBERT+Prophet
-(%)</t>
-  </si>
-  <si>
-    <t>FinBERT+Prophet
-(R$)</t>
-  </si>
-  <si>
-    <t>Como ler: a coluna amarela é o que o investidor faria SEM modelo algum — comprar e segurar. Ela venceu os dois modelos em 8 dos 10 papéis. O motivo é simples: os modelos saem do mercado nos dias em que preveem queda, e acabam perdendo as altas. RESSALVA: não inclui corretagem, imposto de renda nem spread; e, com o acerto perto de cara-ou-coroa, o resultado em reais é em boa parte sorte.</t>
+(sem modelo)</t>
+  </si>
+  <si>
+    <t>+29.1%  (R$ +118.992)</t>
+  </si>
+  <si>
+    <t>+36.1%  (R$ +147.528)</t>
+  </si>
+  <si>
+    <t>+18.8%  (R$ +76.632)</t>
+  </si>
+  <si>
+    <t>-14.5%  (R$ -59.360)</t>
+  </si>
+  <si>
+    <t>-6.1%  (R$ -25.071)</t>
+  </si>
+  <si>
+    <t>+11.4%  (R$ +46.469)</t>
+  </si>
+  <si>
+    <t>+17.9%  (R$ +73.085)</t>
+  </si>
+  <si>
+    <t>+68.3%  (R$ +252.989)</t>
+  </si>
+  <si>
+    <t>+54.9%  (R$ +203.149)</t>
+  </si>
+  <si>
+    <t>+45.3%  (R$ +167.609)</t>
+  </si>
+  <si>
+    <t>-6.7%  (R$ -24.609)</t>
+  </si>
+  <si>
+    <t>+11.0%  (R$ +40.854)</t>
+  </si>
+  <si>
+    <t>+24.9%  (R$ +92.101)</t>
+  </si>
+  <si>
+    <t>+71.0%  (R$ +238.594)</t>
+  </si>
+  <si>
+    <t>+65.2%  (R$ +219.306)</t>
+  </si>
+  <si>
+    <t>+67.9%  (R$ +228.098)</t>
+  </si>
+  <si>
+    <t>+63.9%  (R$ +214.865)</t>
+  </si>
+  <si>
+    <t>+46.9%  (R$ +157.529)</t>
+  </si>
+  <si>
+    <t>+11.5%  (R$ +38.611)</t>
+  </si>
+  <si>
+    <t>+11.9%  (R$ +39.956)</t>
+  </si>
+  <si>
+    <t>+81.1%  (R$ +1.270.237)</t>
+  </si>
+  <si>
+    <t>+57.7%  (R$ +903.756)</t>
+  </si>
+  <si>
+    <t>+71.7%  (R$ +1.122.325)</t>
+  </si>
+  <si>
+    <t>+8.6%  (R$ +134.599)</t>
+  </si>
+  <si>
+    <t>+10.7%  (R$ +166.895)</t>
+  </si>
+  <si>
+    <t>+38.3%  (R$ +600.067)</t>
+  </si>
+  <si>
+    <t>+38.6%  (R$ +604.477)</t>
+  </si>
+  <si>
+    <t>+58.9%  (R$ +79.690)</t>
+  </si>
+  <si>
+    <t>+4.2%  (R$ +5.640)</t>
+  </si>
+  <si>
+    <t>-4.7%  (R$ -6.348)</t>
+  </si>
+  <si>
+    <t>-3.8%  (R$ -5.185)</t>
+  </si>
+  <si>
+    <t>-2.1%  (R$ -2.816)</t>
+  </si>
+  <si>
+    <t>-1.0%  (R$ -1.299)</t>
+  </si>
+  <si>
+    <t>-3.2%  (R$ -4.275)</t>
+  </si>
+  <si>
+    <t>+51.1%  (R$ +150.506)</t>
+  </si>
+  <si>
+    <t>+12.6%  (R$ +37.061)</t>
+  </si>
+  <si>
+    <t>+8.9%  (R$ +26.161)</t>
+  </si>
+  <si>
+    <t>+65.8%  (R$ +193.777)</t>
+  </si>
+  <si>
+    <t>+63.5%  (R$ +186.984)</t>
+  </si>
+  <si>
+    <t>+20.5%  (R$ +60.233)</t>
+  </si>
+  <si>
+    <t>+23.9%  (R$ +70.266)</t>
+  </si>
+  <si>
+    <t>+76.7%  (R$ +82.878)</t>
+  </si>
+  <si>
+    <t>+17.1%  (R$ +18.465)</t>
+  </si>
+  <si>
+    <t>+18.7%  (R$ +20.225)</t>
+  </si>
+  <si>
+    <t>+15.3%  (R$ +16.538)</t>
+  </si>
+  <si>
+    <t>+23.5%  (R$ +25.377)</t>
+  </si>
+  <si>
+    <t>+42.5%  (R$ +45.933)</t>
+  </si>
+  <si>
+    <t>+44.6%  (R$ +48.245)</t>
+  </si>
+  <si>
+    <t>+75.4%  (R$ +1.303.776)</t>
+  </si>
+  <si>
+    <t>+22.3%  (R$ +385.122)</t>
+  </si>
+  <si>
+    <t>+25.7%  (R$ +443.668)</t>
+  </si>
+  <si>
+    <t>+48.0%  (R$ +830.119)</t>
+  </si>
+  <si>
+    <t>+35.7%  (R$ +616.776)</t>
+  </si>
+  <si>
+    <t>+1.6%  (R$ +26.948)</t>
+  </si>
+  <si>
+    <t>+2.8%  (R$ +48.808)</t>
+  </si>
+  <si>
+    <t>-14.7%  (R$ -5.932)</t>
+  </si>
+  <si>
+    <t>-13.2%  (R$ -5.328)</t>
+  </si>
+  <si>
+    <t>-1.7%  (R$ -681)</t>
+  </si>
+  <si>
+    <t>-21.8%  (R$ -8.796)</t>
+  </si>
+  <si>
+    <t>-16.6%  (R$ -6.715)</t>
+  </si>
+  <si>
+    <t>+23.9%  (R$ +9.649)</t>
+  </si>
+  <si>
+    <t>+19.2%  (R$ +7.739)</t>
+  </si>
+  <si>
+    <t>+40.7%  (R$ +121.565)</t>
+  </si>
+  <si>
+    <t>+12.1%  (R$ +35.984)</t>
+  </si>
+  <si>
+    <t>+6.8%  (R$ +20.173)</t>
+  </si>
+  <si>
+    <t>+25.9%  (R$ +77.179)</t>
+  </si>
+  <si>
+    <t>+24.0%  (R$ +71.737)</t>
+  </si>
+  <si>
+    <t>+10.4%  (R$ +30.948)</t>
+  </si>
+  <si>
+    <t>TOTAL (10 papéis)</t>
+  </si>
+  <si>
+    <t>R$ +3.613.295</t>
+  </si>
+  <si>
+    <t>R$ +1.950.684</t>
+  </si>
+  <si>
+    <t>R$ +2.097.862</t>
+  </si>
+  <si>
+    <t>R$ +1.369.127</t>
+  </si>
+  <si>
+    <t>R$ +1.231.551</t>
+  </si>
+  <si>
+    <t>R$ +949.662</t>
+  </si>
+  <si>
+    <t>R$ +1.011.352</t>
+  </si>
+  <si>
+    <t>Só preço histórico × com o FinBERT — a comparação que os senhores pediram</t>
+  </si>
+  <si>
+    <t>Cada família aparece duas vezes: usando SÓ o histórico de preço, e acrescentando o sentimento do FinBERT. Comparando as duas colunas de cada par, o sentimento melhorou o resultado em 5, 6 e 6 dos 10 papéis (SVM, XGBoost e Prophet) — de novo, o padrão de cara-ou-coroa. O efeito médio fica entre −1,2 e +1,0 ponto percentual.</t>
+  </si>
+  <si>
+    <t>E quem ganha de todos</t>
+  </si>
+  <si>
+    <t>A coluna amarela: comprar e segurar, sem modelo algum, sem custo e sem trabalho. Venceu todos os seis modelos em 7 dos 10 papéis, e no total soma mais que qualquer um deles. Os modelos saem do mercado nos dias em que preveem queda e, num período de bolsa em alta, perdem o que deixaram passar.</t>
+  </si>
+  <si>
+    <t>Ressalva obrigatória</t>
+  </si>
+  <si>
+    <t>Esta conta não inclui corretagem, emolumentos, imposto de renda nem a diferença entre preço de compra e de venda — e os modelos entram e saem do mercado dezenas de vezes, o que na prática só pioraria o resultado deles. E, com o acerto direcional perto de cara-ou-coroa, o resultado em reais é em boa parte SORTE, não habilidade. Serve para dar ordem de grandeza; não é recomendação de investimento.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
-    <numFmt numFmtId="6" formatCode="&quot;R$&quot;\ #,##0;[Red]\-&quot;R$&quot;\ #,##0"/>
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="\+0.0%;\-0.0%"/>
     <numFmt numFmtId="166" formatCode="\+0.00;\-0.00"/>
     <numFmt numFmtId="167" formatCode="&quot;R$&quot;\ #,##0"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -350,6 +602,22 @@
     <font>
       <b/>
       <sz val="10"/>
+      <color rgb="FFC00000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF1F3864"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <color rgb="FFC00000"/>
       <name val="Arial"/>
     </font>
@@ -408,7 +676,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -437,6 +705,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -488,25 +759,31 @@
     <xf numFmtId="167" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="6" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="6" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="167" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="6" fontId="8" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -515,6 +792,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -837,13 +1117,13 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
     </row>
     <row r="4" spans="1:5" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -919,13 +1199,13 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="36" t="s">
+      <c r="A10" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="35"/>
-      <c r="C10" s="35"/>
-      <c r="D10" s="35"/>
-      <c r="E10" s="35"/>
+      <c r="B10" s="38"/>
+      <c r="C10" s="38"/>
+      <c r="D10" s="38"/>
+      <c r="E10" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -938,33 +1218,35 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="6" width="13" customWidth="1"/>
-    <col min="7" max="8" width="12" customWidth="1"/>
+    <col min="2" max="3" width="15" customWidth="1"/>
+    <col min="4" max="7" width="13" customWidth="1"/>
+    <col min="8" max="9" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="37" t="s">
+    <row r="2" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-    </row>
-    <row r="4" spans="1:8" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
+    </row>
+    <row r="4" spans="1:10" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>26</v>
       </c>
@@ -989,329 +1271,456 @@
       <c r="H4" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I4" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B5" s="10">
         <v>0.50600000000000001</v>
       </c>
       <c r="C5" s="11">
+        <v>0.50604490500863553</v>
+      </c>
+      <c r="D5" s="12">
         <v>0.50780000000000003</v>
       </c>
-      <c r="D5" s="12">
+      <c r="E5" s="13">
         <v>0.48880000000000001</v>
       </c>
-      <c r="E5" s="12">
+      <c r="F5" s="13">
         <v>0.46460000000000001</v>
       </c>
-      <c r="F5" s="12">
+      <c r="G5" s="13">
         <v>0.49049999999999999</v>
       </c>
-      <c r="G5" s="12">
+      <c r="H5" s="13">
         <v>0.50260000000000005</v>
       </c>
-      <c r="H5" s="12">
+      <c r="I5" s="13">
         <v>0.50260000000000005</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" s="14">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="10">
         <v>0.53369999999999995</v>
       </c>
       <c r="C6" s="15">
+        <v>0.46632124352331611</v>
+      </c>
+      <c r="D6" s="16">
         <v>0.4819</v>
       </c>
-      <c r="D6" s="15">
+      <c r="E6" s="16">
         <v>0.47670000000000001</v>
       </c>
-      <c r="E6" s="15">
+      <c r="F6" s="16">
         <v>0.48699999999999999</v>
       </c>
-      <c r="F6" s="15">
+      <c r="G6" s="16">
         <v>0.50429999999999997</v>
       </c>
-      <c r="G6" s="15">
+      <c r="H6" s="16">
         <v>0.49909999999999999</v>
       </c>
-      <c r="H6" s="15">
+      <c r="I6" s="16">
         <v>0.49909999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B7" s="10">
         <v>0.53200000000000003</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="11">
+        <v>0.53195164075993095</v>
+      </c>
+      <c r="D7" s="13">
         <v>0.5181</v>
       </c>
-      <c r="D7" s="12">
+      <c r="E7" s="13">
         <v>0.52159999999999995</v>
       </c>
-      <c r="E7" s="12">
+      <c r="F7" s="13">
         <v>0.5181</v>
       </c>
-      <c r="F7" s="12">
+      <c r="G7" s="13">
         <v>0.51639999999999997</v>
       </c>
-      <c r="G7" s="12">
+      <c r="H7" s="13">
         <v>0.47670000000000001</v>
       </c>
-      <c r="H7" s="12">
+      <c r="I7" s="13">
         <v>0.47839999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="14">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="10">
         <v>0.50780000000000003</v>
       </c>
       <c r="C8" s="15">
+        <v>0.50777202072538863</v>
+      </c>
+      <c r="D8" s="16">
         <v>0.49569999999999997</v>
       </c>
-      <c r="D8" s="15">
+      <c r="E8" s="16">
         <v>0.50600000000000001</v>
       </c>
-      <c r="E8" s="15">
+      <c r="F8" s="16">
         <v>0.45600000000000002</v>
       </c>
-      <c r="F8" s="15">
+      <c r="G8" s="16">
         <v>0.45250000000000001</v>
       </c>
-      <c r="G8" s="15">
+      <c r="H8" s="16">
         <v>0.50260000000000005</v>
       </c>
-      <c r="H8" s="15">
+      <c r="I8" s="16">
         <v>0.50260000000000005</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B9" s="10">
         <v>0.52159999999999995</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="11">
+        <v>0.47841105354058722</v>
+      </c>
+      <c r="D9" s="13">
         <v>0.49740000000000001</v>
       </c>
-      <c r="D9" s="12">
+      <c r="E9" s="13">
         <v>0.48010000000000003</v>
       </c>
-      <c r="E9" s="12">
+      <c r="F9" s="13">
         <v>0.50949999999999995</v>
       </c>
-      <c r="F9" s="12">
+      <c r="G9" s="13">
         <v>0.49399999999999999</v>
       </c>
-      <c r="G9" s="12">
+      <c r="H9" s="13">
         <v>0.46289999999999998</v>
       </c>
-      <c r="H9" s="12">
+      <c r="I9" s="13">
         <v>0.45939999999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" s="14">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="10">
         <v>0.50600000000000001</v>
       </c>
       <c r="C10" s="15">
+        <v>0.49395509499136442</v>
+      </c>
+      <c r="D10" s="16">
         <v>0.49220000000000003</v>
       </c>
-      <c r="D10" s="15">
+      <c r="E10" s="16">
         <v>0.50260000000000005</v>
       </c>
-      <c r="E10" s="11">
+      <c r="F10" s="12">
         <v>0.52329999999999999</v>
       </c>
-      <c r="F10" s="11">
+      <c r="G10" s="12">
         <v>0.52849999999999997</v>
       </c>
-      <c r="G10" s="15">
+      <c r="H10" s="16">
         <v>0.48880000000000001</v>
       </c>
-      <c r="H10" s="15">
+      <c r="I10" s="16">
         <v>0.48880000000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B11" s="10">
         <v>0.5181</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="11">
+        <v>0.48186528497409331</v>
+      </c>
+      <c r="D11" s="13">
         <v>0.51639999999999997</v>
       </c>
-      <c r="D11" s="12">
+      <c r="E11" s="13">
         <v>0.50600000000000001</v>
       </c>
-      <c r="E11" s="12">
+      <c r="F11" s="13">
         <v>0.50429999999999997</v>
       </c>
-      <c r="F11" s="12">
+      <c r="G11" s="13">
         <v>0.51470000000000005</v>
       </c>
-      <c r="G11" s="12">
+      <c r="H11" s="13">
         <v>0.51119999999999999</v>
       </c>
-      <c r="H11" s="12">
+      <c r="I11" s="13">
         <v>0.51300000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="B12" s="14">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="10">
         <v>0.52680000000000005</v>
       </c>
       <c r="C12" s="15">
+        <v>0.47322970639032808</v>
+      </c>
+      <c r="D12" s="16">
         <v>0.48699999999999999</v>
       </c>
-      <c r="D12" s="15">
+      <c r="E12" s="16">
         <v>0.49909999999999999</v>
       </c>
-      <c r="E12" s="15">
+      <c r="F12" s="16">
         <v>0.52159999999999995</v>
       </c>
-      <c r="F12" s="15">
+      <c r="G12" s="16">
         <v>0.49569999999999997</v>
       </c>
-      <c r="G12" s="15">
+      <c r="H12" s="16">
         <v>0.46460000000000001</v>
       </c>
-      <c r="H12" s="15">
+      <c r="I12" s="16">
         <v>0.46629999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B13" s="10">
         <v>0.50260000000000005</v>
       </c>
       <c r="C13" s="11">
+        <v>0.50259067357512954</v>
+      </c>
+      <c r="D13" s="12">
         <v>0.50600000000000001</v>
       </c>
-      <c r="D13" s="11">
+      <c r="E13" s="12">
         <v>0.51300000000000001</v>
       </c>
-      <c r="E13" s="12">
+      <c r="F13" s="13">
         <v>0.47670000000000001</v>
       </c>
-      <c r="F13" s="12">
+      <c r="G13" s="13">
         <v>0.47839999999999999</v>
       </c>
-      <c r="G13" s="11">
+      <c r="H13" s="12">
         <v>0.50949999999999995</v>
       </c>
-      <c r="H13" s="11">
+      <c r="I13" s="12">
         <v>0.50780000000000003</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" s="14">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="10">
         <v>0.50090000000000001</v>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="15">
+        <v>0.50086355785837655</v>
+      </c>
+      <c r="D14" s="12">
         <v>0.50780000000000003</v>
       </c>
-      <c r="D14" s="11">
+      <c r="E14" s="12">
         <v>0.50260000000000005</v>
       </c>
-      <c r="E14" s="11">
+      <c r="F14" s="12">
         <v>0.53200000000000003</v>
       </c>
-      <c r="F14" s="11">
+      <c r="G14" s="12">
         <v>0.52500000000000002</v>
       </c>
-      <c r="G14" s="15">
+      <c r="H14" s="16">
         <v>0.50090000000000001</v>
       </c>
-      <c r="H14" s="15">
+      <c r="I14" s="16">
         <v>0.50090000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" s="17" t="s">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="D16" s="17" t="s">
+      <c r="D16" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="E16" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="F16" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="G16" s="17" t="s">
+      <c r="E16" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="H16" s="17" t="s">
+      <c r="F16" s="18" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="16" t="s">
+      <c r="G16" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="H16" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="C17" s="18" t="s">
+      <c r="I16" s="18" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="17" t="s">
         <v>49</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F17" s="18" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G17" s="18" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H17" s="18" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="37" t="s">
-        <v>50</v>
-      </c>
-      <c r="B19" s="35"/>
-      <c r="C19" s="35"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="35"/>
-      <c r="H19" s="35"/>
+        <v>52</v>
+      </c>
+      <c r="I17" s="18" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="F18" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="G18" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="H18" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="I18" s="19" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="40" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20" s="38"/>
+      <c r="C20" s="38"/>
+      <c r="D20" s="38"/>
+      <c r="E20" s="38"/>
+      <c r="F20" s="38"/>
+      <c r="G20" s="38"/>
+      <c r="H20" s="38"/>
+      <c r="I20" s="38"/>
+    </row>
+    <row r="21" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="41" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21" s="38"/>
+      <c r="C21" s="38"/>
+      <c r="D21" s="38"/>
+      <c r="E21" s="38"/>
+      <c r="F21" s="38"/>
+      <c r="G21" s="38"/>
+      <c r="H21" s="38"/>
+      <c r="I21" s="38"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="40" t="s">
+        <v>57</v>
+      </c>
+      <c r="B23" s="38"/>
+      <c r="C23" s="38"/>
+      <c r="D23" s="38"/>
+      <c r="E23" s="38"/>
+      <c r="F23" s="38"/>
+      <c r="G23" s="38"/>
+      <c r="H23" s="38"/>
+      <c r="I23" s="38"/>
+    </row>
+    <row r="24" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="B24" s="38"/>
+      <c r="C24" s="38"/>
+      <c r="D24" s="38"/>
+      <c r="E24" s="38"/>
+      <c r="F24" s="38"/>
+      <c r="G24" s="38"/>
+      <c r="H24" s="38"/>
+      <c r="I24" s="38"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="40" t="s">
+        <v>59</v>
+      </c>
+      <c r="B26" s="38"/>
+      <c r="C26" s="38"/>
+      <c r="D26" s="38"/>
+      <c r="E26" s="38"/>
+      <c r="F26" s="38"/>
+      <c r="G26" s="38"/>
+      <c r="H26" s="38"/>
+      <c r="I26" s="38"/>
+    </row>
+    <row r="27" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="41" t="s">
+        <v>60</v>
+      </c>
+      <c r="B27" s="38"/>
+      <c r="C27" s="38"/>
+      <c r="D27" s="38"/>
+      <c r="E27" s="38"/>
+      <c r="F27" s="38"/>
+      <c r="G27" s="38"/>
+      <c r="H27" s="38"/>
+      <c r="I27" s="38"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A2:H2"/>
+  <mergeCells count="7">
+    <mergeCell ref="A26:I26"/>
+    <mergeCell ref="A21:I21"/>
+    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="A27:I27"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A20:I20"/>
+    <mergeCell ref="A24:I24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1330,248 +1739,248 @@
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="37" t="s">
-        <v>52</v>
-      </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
+      <c r="A2" s="41" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
     </row>
     <row r="4" spans="1:6" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="B5" s="19">
+        <v>35</v>
+      </c>
+      <c r="B5" s="20">
         <v>0.88879999999999992</v>
       </c>
-      <c r="C5" s="19">
+      <c r="C5" s="20">
         <v>0.88290000000000002</v>
       </c>
-      <c r="D5" s="20">
+      <c r="D5" s="21">
         <v>-0.9556</v>
       </c>
-      <c r="E5" s="20">
+      <c r="E5" s="21">
         <v>-0.96799999999999997</v>
       </c>
-      <c r="F5" s="21" t="s">
-        <v>56</v>
+      <c r="F5" s="22" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" s="19">
+      <c r="A6" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="20">
         <v>0.87180000000000002</v>
       </c>
-      <c r="C6" s="19">
+      <c r="C6" s="20">
         <v>0.87190000000000001</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="21">
         <v>-2.5586000000000002</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="21">
         <v>-2.5550999999999999</v>
       </c>
-      <c r="F6" s="22" t="s">
-        <v>56</v>
+      <c r="F6" s="23" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" s="19">
+        <v>37</v>
+      </c>
+      <c r="B7" s="20">
         <v>0.87760000000000005</v>
       </c>
-      <c r="C7" s="19">
+      <c r="C7" s="20">
         <v>0.87730000000000008</v>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="21">
         <v>-1.6029</v>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="21">
         <v>-1.5940000000000001</v>
       </c>
-      <c r="F7" s="21" t="s">
-        <v>56</v>
+      <c r="F7" s="22" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="19">
+      <c r="A8" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="20">
         <v>0.877</v>
       </c>
-      <c r="C8" s="19">
+      <c r="C8" s="20">
         <v>0.87599999999999989</v>
       </c>
-      <c r="D8" s="20">
+      <c r="D8" s="21">
         <v>-1.5553999999999999</v>
       </c>
-      <c r="E8" s="20">
+      <c r="E8" s="21">
         <v>-1.55</v>
       </c>
-      <c r="F8" s="22" t="s">
-        <v>56</v>
+      <c r="F8" s="23" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="19">
+        <v>39</v>
+      </c>
+      <c r="B9" s="20">
         <v>0.86290000000000011</v>
       </c>
-      <c r="C9" s="19">
+      <c r="C9" s="20">
         <v>0.86290000000000011</v>
       </c>
-      <c r="D9" s="20">
+      <c r="D9" s="21">
         <v>-0.47460000000000002</v>
       </c>
-      <c r="E9" s="20">
+      <c r="E9" s="21">
         <v>-0.4839</v>
       </c>
-      <c r="F9" s="21" t="s">
-        <v>56</v>
+      <c r="F9" s="22" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" s="19">
+      <c r="A10" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="20">
         <v>0.88090000000000002</v>
       </c>
-      <c r="C10" s="19">
+      <c r="C10" s="20">
         <v>0.87970000000000004</v>
       </c>
-      <c r="D10" s="20">
+      <c r="D10" s="21">
         <v>-0.88719999999999999</v>
       </c>
-      <c r="E10" s="20">
+      <c r="E10" s="21">
         <v>-0.90159999999999996</v>
       </c>
-      <c r="F10" s="22" t="s">
-        <v>56</v>
+      <c r="F10" s="23" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="B11" s="19">
+        <v>41</v>
+      </c>
+      <c r="B11" s="20">
         <v>0.85560000000000003</v>
       </c>
-      <c r="C11" s="19">
+      <c r="C11" s="20">
         <v>0.85580000000000001</v>
       </c>
-      <c r="D11" s="20">
+      <c r="D11" s="21">
         <v>-2.5453000000000001</v>
       </c>
-      <c r="E11" s="20">
+      <c r="E11" s="21">
         <v>-2.6482000000000001</v>
       </c>
-      <c r="F11" s="21" t="s">
-        <v>56</v>
+      <c r="F11" s="22" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="B12" s="19">
+      <c r="A12" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="20">
         <v>0.83010000000000006</v>
       </c>
-      <c r="C12" s="19">
+      <c r="C12" s="20">
         <v>0.8306</v>
       </c>
-      <c r="D12" s="20">
+      <c r="D12" s="21">
         <v>-0.73739999999999994</v>
       </c>
-      <c r="E12" s="20">
+      <c r="E12" s="21">
         <v>-0.73970000000000002</v>
       </c>
-      <c r="F12" s="22" t="s">
-        <v>56</v>
+      <c r="F12" s="23" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B13" s="19">
+        <v>43</v>
+      </c>
+      <c r="B13" s="20">
         <v>0.85849999999999993</v>
       </c>
-      <c r="C13" s="19">
+      <c r="C13" s="20">
         <v>0.85959999999999992</v>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="21">
         <v>-0.76489999999999991</v>
       </c>
-      <c r="E13" s="20">
+      <c r="E13" s="21">
         <v>-0.7208</v>
       </c>
-      <c r="F13" s="21" t="s">
-        <v>56</v>
+      <c r="F13" s="22" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" s="19">
+      <c r="A14" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="20">
         <v>0.9274</v>
       </c>
-      <c r="C14" s="19">
+      <c r="C14" s="20">
         <v>0.92730000000000001</v>
       </c>
-      <c r="D14" s="20">
+      <c r="D14" s="21">
         <v>-0.48680000000000001</v>
       </c>
-      <c r="E14" s="20">
+      <c r="E14" s="21">
         <v>-0.47739999999999999</v>
       </c>
-      <c r="F14" s="22" t="s">
-        <v>56</v>
+      <c r="F14" s="23" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="B16" s="35"/>
-      <c r="C16" s="35"/>
-      <c r="D16" s="35"/>
-      <c r="E16" s="35"/>
-      <c r="F16" s="35"/>
+      <c r="A16" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="B16" s="38"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="38"/>
+      <c r="F16" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1596,12 +2005,12 @@
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="23" t="s">
-        <v>59</v>
+      <c r="A2" s="24" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -1609,250 +2018,250 @@
         <v>26</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="B5" s="24">
+        <v>35</v>
+      </c>
+      <c r="B5" s="25">
         <v>-1.9000000000000019</v>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="26">
         <v>2.5899999999999981</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="25">
         <v>0</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="25">
         <v>-0.5899999999999892</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="25">
         <v>-1.2399999999999951</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" s="24">
+      <c r="A6" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="25">
         <v>-0.51999999999999824</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="26">
         <v>1.729999999999998</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="25">
         <v>0</v>
       </c>
-      <c r="E6" s="25">
+      <c r="E6" s="26">
         <v>9.9999999999909051E-3</v>
       </c>
-      <c r="F6" s="25">
+      <c r="F6" s="26">
         <v>0.35000000000002268</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" s="25">
+        <v>37</v>
+      </c>
+      <c r="B7" s="26">
         <v>0.34999999999999482</v>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="25">
         <v>-0.17000000000000351</v>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="26">
         <v>0.1699999999999979</v>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="25">
         <v>-3.000000000000114E-2</v>
       </c>
-      <c r="F7" s="25">
+      <c r="F7" s="26">
         <v>0.88999999999998636</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="25">
+      <c r="A8" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="26">
         <v>1.0300000000000029</v>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="25">
         <v>-0.35000000000000031</v>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="25">
         <v>0</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="25">
         <v>-0.1000000000000085</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="26">
         <v>0.53999999999999204</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="24">
+        <v>39</v>
+      </c>
+      <c r="B9" s="25">
         <v>-1.729999999999998</v>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="25">
         <v>-1.549999999999996</v>
       </c>
-      <c r="D9" s="24">
+      <c r="D9" s="25">
         <v>-0.35000000000000031</v>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="25">
         <v>0</v>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="25">
         <v>-0.92999999999999972</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" s="25">
+      <c r="A10" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="26">
         <v>1.040000000000002</v>
       </c>
-      <c r="C10" s="25">
+      <c r="C10" s="26">
         <v>0.51999999999999824</v>
       </c>
-      <c r="D10" s="24">
+      <c r="D10" s="25">
         <v>0</v>
       </c>
-      <c r="E10" s="24">
+      <c r="E10" s="25">
         <v>-0.12000000000000451</v>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="25">
         <v>-1.4399999999999979</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="B11" s="24">
+        <v>41</v>
+      </c>
+      <c r="B11" s="25">
         <v>-1.039999999999996</v>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="26">
         <v>1.040000000000008</v>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="26">
         <v>0.18000000000000241</v>
       </c>
-      <c r="E11" s="25">
+      <c r="E11" s="26">
         <v>1.9999999999996021E-2</v>
       </c>
-      <c r="F11" s="24">
+      <c r="F11" s="25">
         <v>-10.28999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="B12" s="25">
+      <c r="A12" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="26">
         <v>1.21</v>
       </c>
-      <c r="C12" s="24">
+      <c r="C12" s="25">
         <v>-2.5899999999999981</v>
       </c>
-      <c r="D12" s="25">
+      <c r="D12" s="26">
         <v>0.1699999999999979</v>
       </c>
-      <c r="E12" s="25">
+      <c r="E12" s="26">
         <v>4.9999999999997158E-2</v>
       </c>
-      <c r="F12" s="24">
+      <c r="F12" s="25">
         <v>-0.23000000000000401</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B13" s="25">
+        <v>43</v>
+      </c>
+      <c r="B13" s="26">
         <v>0.70000000000000062</v>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="26">
         <v>0.1699999999999979</v>
       </c>
-      <c r="D13" s="24">
+      <c r="D13" s="25">
         <v>-0.16999999999999241</v>
       </c>
-      <c r="E13" s="25">
+      <c r="E13" s="26">
         <v>0.1099999999999994</v>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="26">
         <v>4.4099999999999966</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" s="24">
+      <c r="A14" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="25">
         <v>-0.51999999999999824</v>
       </c>
-      <c r="C14" s="24">
+      <c r="C14" s="25">
         <v>-0.70000000000000062</v>
       </c>
-      <c r="D14" s="24">
+      <c r="D14" s="25">
         <v>0</v>
       </c>
-      <c r="E14" s="24">
+      <c r="E14" s="25">
         <v>-9.9999999999909051E-3</v>
       </c>
-      <c r="F14" s="25">
+      <c r="F14" s="26">
         <v>0.93999999999999773</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="B16" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="C16" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="D16" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="E16" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="F16" s="17" t="s">
-        <v>66</v>
+      <c r="A16" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="E16" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="F16" s="18" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="37" t="s">
-        <v>68</v>
-      </c>
-      <c r="B18" s="35"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="35"/>
+      <c r="A18" s="41" t="s">
+        <v>77</v>
+      </c>
+      <c r="B18" s="38"/>
+      <c r="C18" s="38"/>
+      <c r="D18" s="38"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1864,338 +2273,462 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="15" customWidth="1"/>
+    <col min="2" max="9" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-    </row>
-    <row r="4" spans="1:8" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="41" t="s">
+        <v>79</v>
+      </c>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+    </row>
+    <row r="4" spans="1:9" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>74</v>
+        <v>30</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>75</v>
+        <v>31</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="B5" s="26">
+        <v>35</v>
+      </c>
+      <c r="B5" s="27">
         <v>408786.4</v>
       </c>
-      <c r="C5" s="27">
-        <v>0.29110000000000003</v>
-      </c>
-      <c r="D5" s="28">
-        <v>118991.99</v>
-      </c>
-      <c r="E5" s="29">
-        <v>0.1875</v>
-      </c>
-      <c r="F5" s="30">
-        <v>76632.33</v>
-      </c>
-      <c r="G5" s="29">
-        <v>0.17879999999999999</v>
-      </c>
-      <c r="H5" s="30">
-        <v>73085.490000000005</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
-        <v>35</v>
+      <c r="C5" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="D5" s="29" t="s">
+        <v>83</v>
+      </c>
+      <c r="E5" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="F5" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="G5" s="30" t="s">
+        <v>86</v>
+      </c>
+      <c r="H5" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="I5" s="29" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="14" t="s">
+        <v>36</v>
       </c>
       <c r="B6" s="31">
         <v>370218.56</v>
       </c>
-      <c r="C6" s="27">
-        <v>0.68340000000000001</v>
-      </c>
-      <c r="D6" s="28">
-        <v>252988.89</v>
-      </c>
-      <c r="E6" s="32">
-        <v>0.45269999999999999</v>
-      </c>
-      <c r="F6" s="33">
-        <v>167609.29</v>
-      </c>
-      <c r="G6" s="32">
-        <v>0.24879999999999999</v>
-      </c>
-      <c r="H6" s="33">
-        <v>92101.1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C6" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="D6" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="E6" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="F6" s="33" t="s">
+        <v>92</v>
+      </c>
+      <c r="G6" s="32" t="s">
+        <v>93</v>
+      </c>
+      <c r="H6" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="I6" s="32" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" s="26">
+        <v>37</v>
+      </c>
+      <c r="B7" s="27">
         <v>336097.94</v>
       </c>
-      <c r="C7" s="27">
-        <v>0.70989999999999998</v>
-      </c>
-      <c r="D7" s="28">
-        <v>238593.9</v>
-      </c>
-      <c r="E7" s="29">
-        <v>0.67870000000000008</v>
-      </c>
-      <c r="F7" s="30">
-        <v>228097.52</v>
-      </c>
-      <c r="G7" s="29">
-        <v>0.11890000000000001</v>
-      </c>
-      <c r="H7" s="30">
-        <v>39956.01</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
-        <v>37</v>
+      <c r="C7" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="D7" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="E7" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="F7" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="G7" s="29" t="s">
+        <v>99</v>
+      </c>
+      <c r="H7" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="I7" s="29" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
+        <v>38</v>
       </c>
       <c r="B8" s="31">
         <v>1566110.66</v>
       </c>
-      <c r="C8" s="27">
-        <v>0.81110000000000004</v>
-      </c>
-      <c r="D8" s="28">
-        <v>1270236.96</v>
-      </c>
-      <c r="E8" s="32">
-        <v>0.71660000000000001</v>
-      </c>
-      <c r="F8" s="33">
-        <v>1122324.95</v>
-      </c>
-      <c r="G8" s="32">
-        <v>0.38600000000000001</v>
-      </c>
-      <c r="H8" s="33">
-        <v>604477.18000000005</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C8" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="D8" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="E8" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="F8" s="32" t="s">
+        <v>105</v>
+      </c>
+      <c r="G8" s="32" t="s">
+        <v>106</v>
+      </c>
+      <c r="H8" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="I8" s="32" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="26">
+        <v>39</v>
+      </c>
+      <c r="B9" s="27">
         <v>135402.23999999999</v>
       </c>
-      <c r="C9" s="27">
-        <v>0.58850000000000002</v>
-      </c>
-      <c r="D9" s="28">
-        <v>79689.66</v>
-      </c>
-      <c r="E9" s="29">
-        <v>-2.0799999999999999E-2</v>
-      </c>
-      <c r="F9" s="30">
-        <v>-2815.95</v>
-      </c>
-      <c r="G9" s="29">
-        <v>-3.1600000000000003E-2</v>
-      </c>
-      <c r="H9" s="30">
-        <v>-4275.16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
-        <v>39</v>
+      <c r="C9" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="D9" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="E9" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="F9" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="G9" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="H9" s="30" t="s">
+        <v>114</v>
+      </c>
+      <c r="I9" s="30" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="s">
+        <v>40</v>
       </c>
       <c r="B10" s="31">
         <v>294452.08</v>
       </c>
-      <c r="C10" s="27">
-        <v>0.5111</v>
-      </c>
-      <c r="D10" s="28">
-        <v>150505.91</v>
-      </c>
-      <c r="E10" s="32">
-        <v>0.63500000000000001</v>
-      </c>
-      <c r="F10" s="33">
-        <v>186984.3</v>
-      </c>
-      <c r="G10" s="32">
-        <v>0.23860000000000001</v>
-      </c>
-      <c r="H10" s="33">
-        <v>70266.289999999994</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C10" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="D10" s="32" t="s">
+        <v>117</v>
+      </c>
+      <c r="E10" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="F10" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="G10" s="32" t="s">
+        <v>120</v>
+      </c>
+      <c r="H10" s="32" t="s">
+        <v>121</v>
+      </c>
+      <c r="I10" s="32" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="B11" s="26">
+        <v>41</v>
+      </c>
+      <c r="B11" s="27">
         <v>108098.9</v>
       </c>
-      <c r="C11" s="27">
-        <v>0.76670000000000005</v>
-      </c>
-      <c r="D11" s="28">
-        <v>82878.259999999995</v>
-      </c>
-      <c r="E11" s="29">
-        <v>0.23480000000000001</v>
-      </c>
-      <c r="F11" s="30">
-        <v>25376.68</v>
-      </c>
-      <c r="G11" s="29">
-        <v>0.44629999999999997</v>
-      </c>
-      <c r="H11" s="30">
-        <v>48245.14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
-        <v>41</v>
+      <c r="C11" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="D11" s="29" t="s">
+        <v>124</v>
+      </c>
+      <c r="E11" s="29" t="s">
+        <v>125</v>
+      </c>
+      <c r="F11" s="29" t="s">
+        <v>126</v>
+      </c>
+      <c r="G11" s="29" t="s">
+        <v>127</v>
+      </c>
+      <c r="H11" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="I11" s="29" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="14" t="s">
+        <v>42</v>
       </c>
       <c r="B12" s="31">
         <v>1728873.12</v>
       </c>
-      <c r="C12" s="27">
-        <v>0.75409999999999999</v>
-      </c>
-      <c r="D12" s="28">
-        <v>1303775.98</v>
-      </c>
-      <c r="E12" s="32">
-        <v>0.35680000000000001</v>
-      </c>
-      <c r="F12" s="33">
-        <v>616776.31999999995</v>
-      </c>
-      <c r="G12" s="32">
-        <v>2.8199999999999999E-2</v>
-      </c>
-      <c r="H12" s="33">
-        <v>48807.71</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C12" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="D12" s="32" t="s">
+        <v>131</v>
+      </c>
+      <c r="E12" s="32" t="s">
+        <v>132</v>
+      </c>
+      <c r="F12" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="G12" s="32" t="s">
+        <v>134</v>
+      </c>
+      <c r="H12" s="32" t="s">
+        <v>135</v>
+      </c>
+      <c r="I12" s="32" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B13" s="26">
+        <v>43</v>
+      </c>
+      <c r="B13" s="27">
         <v>40389.550000000003</v>
       </c>
-      <c r="C13" s="27">
-        <v>-0.1469</v>
-      </c>
-      <c r="D13" s="28">
-        <v>-5932.35</v>
-      </c>
-      <c r="E13" s="29">
-        <v>-1.6899999999999998E-2</v>
-      </c>
-      <c r="F13" s="30">
-        <v>-681.16</v>
-      </c>
-      <c r="G13" s="29">
-        <v>0.19159999999999999</v>
-      </c>
-      <c r="H13" s="30">
-        <v>7739.49</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
-        <v>43</v>
+      <c r="C13" s="34" t="s">
+        <v>137</v>
+      </c>
+      <c r="D13" s="30" t="s">
+        <v>138</v>
+      </c>
+      <c r="E13" s="30" t="s">
+        <v>139</v>
+      </c>
+      <c r="F13" s="30" t="s">
+        <v>140</v>
+      </c>
+      <c r="G13" s="30" t="s">
+        <v>141</v>
+      </c>
+      <c r="H13" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="I13" s="29" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="14" t="s">
+        <v>44</v>
       </c>
       <c r="B14" s="31">
         <v>298478.46999999997</v>
       </c>
-      <c r="C14" s="27">
-        <v>0.4073</v>
-      </c>
-      <c r="D14" s="28">
-        <v>121565.47</v>
-      </c>
-      <c r="E14" s="32">
-        <v>0.24030000000000001</v>
-      </c>
-      <c r="F14" s="33">
-        <v>71736.639999999999</v>
-      </c>
-      <c r="G14" s="32">
-        <v>0.1037</v>
-      </c>
-      <c r="H14" s="33">
-        <v>30948.34</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="37" t="s">
-        <v>78</v>
-      </c>
-      <c r="B16" s="35"/>
-      <c r="C16" s="35"/>
-      <c r="D16" s="35"/>
-      <c r="E16" s="35"/>
-      <c r="F16" s="35"/>
-      <c r="G16" s="35"/>
-      <c r="H16" s="35"/>
+      <c r="C14" s="28" t="s">
+        <v>144</v>
+      </c>
+      <c r="D14" s="32" t="s">
+        <v>145</v>
+      </c>
+      <c r="E14" s="32" t="s">
+        <v>146</v>
+      </c>
+      <c r="F14" s="32" t="s">
+        <v>147</v>
+      </c>
+      <c r="G14" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="H14" s="32" t="s">
+        <v>149</v>
+      </c>
+      <c r="I14" s="32" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="C16" s="35" t="s">
+        <v>151</v>
+      </c>
+      <c r="D16" s="36" t="s">
+        <v>152</v>
+      </c>
+      <c r="E16" s="36" t="s">
+        <v>153</v>
+      </c>
+      <c r="F16" s="36" t="s">
+        <v>154</v>
+      </c>
+      <c r="G16" s="36" t="s">
+        <v>155</v>
+      </c>
+      <c r="H16" s="36" t="s">
+        <v>156</v>
+      </c>
+      <c r="I16" s="36" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="40" t="s">
+        <v>158</v>
+      </c>
+      <c r="B18" s="38"/>
+      <c r="C18" s="38"/>
+      <c r="D18" s="38"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="38"/>
+      <c r="G18" s="38"/>
+      <c r="H18" s="38"/>
+      <c r="I18" s="38"/>
+    </row>
+    <row r="19" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="B19" s="38"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="38"/>
+      <c r="E19" s="38"/>
+      <c r="F19" s="38"/>
+      <c r="G19" s="38"/>
+      <c r="H19" s="38"/>
+      <c r="I19" s="38"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="40" t="s">
+        <v>160</v>
+      </c>
+      <c r="B21" s="38"/>
+      <c r="C21" s="38"/>
+      <c r="D21" s="38"/>
+      <c r="E21" s="38"/>
+      <c r="F21" s="38"/>
+      <c r="G21" s="38"/>
+      <c r="H21" s="38"/>
+      <c r="I21" s="38"/>
+    </row>
+    <row r="22" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="41" t="s">
+        <v>161</v>
+      </c>
+      <c r="B22" s="38"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="38"/>
+      <c r="E22" s="38"/>
+      <c r="F22" s="38"/>
+      <c r="G22" s="38"/>
+      <c r="H22" s="38"/>
+      <c r="I22" s="38"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="40" t="s">
+        <v>162</v>
+      </c>
+      <c r="B24" s="38"/>
+      <c r="C24" s="38"/>
+      <c r="D24" s="38"/>
+      <c r="E24" s="38"/>
+      <c r="F24" s="38"/>
+      <c r="G24" s="38"/>
+      <c r="H24" s="38"/>
+      <c r="I24" s="38"/>
+    </row>
+    <row r="25" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="41" t="s">
+        <v>163</v>
+      </c>
+      <c r="B25" s="38"/>
+      <c r="C25" s="38"/>
+      <c r="D25" s="38"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="38"/>
+      <c r="G25" s="38"/>
+      <c r="H25" s="38"/>
+      <c r="I25" s="38"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A16:H16"/>
+  <mergeCells count="7">
+    <mergeCell ref="A25:I25"/>
+    <mergeCell ref="A19:I19"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A18:I18"/>
+    <mergeCell ref="A22:I22"/>
+    <mergeCell ref="A24:I24"/>
+    <mergeCell ref="A21:I21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Mentorias/2026-10-23_Emerson_e_Julio/02_Comparativo_FinBERT.xlsx
+++ b/Mentorias/2026-10-23_Emerson_e_Julio/02_Comparativo_FinBERT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\mestrado\coleta_dados_petr4\Mentorias\2026-10-23_Emerson_e_Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_C784901BED39F3B6DA0ABA36545C7094D030CC6A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_1706DBDB8F2EF3B6DA0ABAF0BC997338D030C21E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -287,8 +287,8 @@
 (médio)</t>
   </si>
   <si>
-    <t>Comprar e segurar
-(sem modelo)</t>
+    <t>NÃO DECIDE NADA
+Comprar e segurar</t>
   </si>
   <si>
     <t>+29.1%  (R$ +118.992)</t>
@@ -525,10 +525,10 @@
     <t>Cada família aparece duas vezes: usando SÓ o histórico de preço, e acrescentando o sentimento do FinBERT. Comparando as duas colunas de cada par, o sentimento melhorou o resultado em 5, 6 e 6 dos 10 papéis (SVM, XGBoost e Prophet) — de novo, o padrão de cara-ou-coroa. O efeito médio fica entre −1,2 e +1,0 ponto percentual.</t>
   </si>
   <si>
-    <t>E quem ganha de todos</t>
-  </si>
-  <si>
-    <t>A coluna amarela: comprar e segurar, sem modelo algum, sem custo e sem trabalho. Venceu todos os seis modelos em 7 dos 10 papéis, e no total soma mais que qualquer um deles. Os modelos saem do mercado nos dias em que preveem queda e, num período de bolsa em alta, perdem o que deixaram passar.</t>
+    <t>A coluna amarela NÃO analisa preço histórico — ela não analisa nada</t>
+  </si>
+  <si>
+    <t>Comprar e segurar significa: comprar no primeiro dia, não mexer em nenhum dia, vender no último. Zero contas, zero decisões. É diferente das colunas 'só preço', que são modelos de verdade decidindo todo dia se ficam no mercado ou saem. Mesmo assim, a coluna amarela venceu os seis modelos em 7 dos 10 papéis. O motivo: a única coisa que um modelo pode fazer aqui é TIRAR o investidor do mercado em alguns dias; como o acerto está perto de cara-ou-coroa, ele tira em dias bons e ruins por igual — e, num período de bolsa em alta, cada dia bom perdido é dinheiro que não volta.</t>
   </si>
   <si>
     <t>Ressalva obrigatória</t>
